--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_los_rios.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_los_rios.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>25.70719087544376</v>
+      </c>
+      <c r="C2">
         <v>28.81165495883375</v>
-      </c>
-      <c r="C2">
-        <v>25.70719087544376</v>
       </c>
       <c r="D2">
         <v>3.47081763067344</v>
       </c>
       <c r="E2">
-        <v>18.6460459261613</v>
+        <v>16.63692913097144</v>
       </c>
       <c r="F2">
         <v>64.71702494286727</v>
       </c>
       <c r="G2">
-        <v>16.63692913097144</v>
+        <v>18.6460459261613</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>29.94854202401373</v>
+      </c>
+      <c r="C3">
         <v>38.07890222984562</v>
-      </c>
-      <c r="C3">
-        <v>29.94854202401373</v>
       </c>
       <c r="D3">
         <v>2.626126126126126</v>
       </c>
       <c r="E3">
-        <v>22.6623111474071</v>
+        <v>17.82360146998775</v>
       </c>
       <c r="F3">
         <v>59.51408738260514</v>
       </c>
       <c r="G3">
-        <v>17.82360146998775</v>
+        <v>22.6623111474071</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>29.69177457596206</v>
+      </c>
+      <c r="C4">
         <v>31.88035746853912</v>
-      </c>
-      <c r="C4">
-        <v>29.69177457596206</v>
       </c>
       <c r="D4">
         <v>3.136727688787186</v>
       </c>
       <c r="E4">
-        <v>19.73134665312112</v>
+        <v>18.3767919629755</v>
       </c>
       <c r="F4">
         <v>61.89186138390338</v>
       </c>
       <c r="G4">
-        <v>18.3767919629755</v>
+        <v>19.73134665312112</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>30.06294256490952</v>
+      </c>
+      <c r="C5">
         <v>31.48701809598741</v>
-      </c>
-      <c r="C5">
-        <v>30.06294256490952</v>
       </c>
       <c r="D5">
         <v>3.175912043978011</v>
       </c>
       <c r="E5">
-        <v>19.49057614571665</v>
+        <v>18.60906832903132</v>
       </c>
       <c r="F5">
         <v>61.90035552525203</v>
       </c>
       <c r="G5">
-        <v>18.60906832903132</v>
+        <v>19.49057614571665</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>27.99492922036763</v>
+      </c>
+      <c r="C6">
         <v>33.76294105218678</v>
-      </c>
-      <c r="C6">
-        <v>27.99492922036763</v>
       </c>
       <c r="D6">
         <v>2.961827284105131</v>
       </c>
       <c r="E6">
-        <v>20.87251828631139</v>
+        <v>17.30668756530826</v>
       </c>
       <c r="F6">
         <v>61.82079414838037</v>
       </c>
       <c r="G6">
-        <v>17.30668756530826</v>
+        <v>20.87251828631139</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>34.0049250055966</v>
+      </c>
+      <c r="C7">
         <v>28.34116856950974</v>
-      </c>
-      <c r="C7">
-        <v>34.0049250055966</v>
       </c>
       <c r="D7">
         <v>3.528436018957346</v>
       </c>
       <c r="E7">
-        <v>17.45725317153889</v>
+        <v>20.94594594594595</v>
       </c>
       <c r="F7">
         <v>61.59680088251518</v>
       </c>
       <c r="G7">
-        <v>20.94594594594595</v>
+        <v>17.45725317153889</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>30.37138483847579</v>
+      </c>
+      <c r="C8">
         <v>34.24635462821236</v>
-      </c>
-      <c r="C8">
-        <v>30.37138483847579</v>
       </c>
       <c r="D8">
         <v>2.920018819101388</v>
       </c>
       <c r="E8">
-        <v>20.80356268963492</v>
+        <v>18.44964275227562</v>
       </c>
       <c r="F8">
         <v>60.74679455808946</v>
       </c>
       <c r="G8">
-        <v>18.44964275227562</v>
+        <v>20.80356268963492</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>30.93216511606901</v>
+      </c>
+      <c r="C9">
         <v>30.4308553879505</v>
-      </c>
-      <c r="C9">
-        <v>30.93216511606901</v>
       </c>
       <c r="D9">
         <v>3.286138319976254</v>
       </c>
       <c r="E9">
-        <v>18.85863024433933</v>
+        <v>19.16930224747404</v>
       </c>
       <c r="F9">
         <v>61.97206750818663</v>
       </c>
       <c r="G9">
-        <v>19.16930224747405</v>
+        <v>18.85863024433933</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>27.78331257783313</v>
+      </c>
+      <c r="C10">
         <v>34.19676214196762</v>
-      </c>
-      <c r="C10">
-        <v>27.78331257783313</v>
       </c>
       <c r="D10">
         <v>2.924253459577567</v>
       </c>
       <c r="E10">
+        <v>17.15230260628892</v>
+      </c>
+      <c r="F10">
+        <v>61.73598831398477</v>
+      </c>
+      <c r="G10">
         <v>21.1117090797263</v>
-      </c>
-      <c r="F10">
-        <v>61.73598831398478</v>
-      </c>
-      <c r="G10">
-        <v>17.15230260628892</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>32.78705969990423</v>
+      </c>
+      <c r="C11">
         <v>29.2220921570714</v>
-      </c>
-      <c r="C11">
-        <v>32.78705969990423</v>
       </c>
       <c r="D11">
         <v>3.422068463219228</v>
       </c>
       <c r="E11">
-        <v>18.03730951129795</v>
+        <v>20.23778244876511</v>
       </c>
       <c r="F11">
         <v>61.72490803993693</v>
       </c>
       <c r="G11">
-        <v>20.23778244876511</v>
+        <v>18.03730951129795</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>32.0562154927221</v>
+      </c>
+      <c r="C12">
         <v>35.18487535552953</v>
-      </c>
-      <c r="C12">
-        <v>32.0562154927221</v>
       </c>
       <c r="D12">
         <v>2.842130290061816</v>
       </c>
       <c r="E12">
-        <v>21.03841536614646</v>
+        <v>19.16766706682673</v>
       </c>
       <c r="F12">
         <v>59.7939175670268</v>
       </c>
       <c r="G12">
-        <v>19.16766706682673</v>
+        <v>21.03841536614646</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>28.46445897489981</v>
+      </c>
+      <c r="C13">
         <v>36.30035857414048</v>
-      </c>
-      <c r="C13">
-        <v>28.46445897489981</v>
       </c>
       <c r="D13">
         <v>2.754793724578733</v>
       </c>
       <c r="E13">
-        <v>22.03162004736607</v>
+        <v>17.27581130384689</v>
       </c>
       <c r="F13">
         <v>60.69256864878705</v>
       </c>
       <c r="G13">
-        <v>17.27581130384689</v>
+        <v>22.03162004736607</v>
       </c>
     </row>
   </sheetData>
